--- a/public/templates/office/EMP_MAN_005_프로젝트_연락처_및_회의체계.xlsx
+++ b/public/templates/office/EMP_MAN_005_프로젝트_연락처_및_회의체계.xlsx
@@ -656,7 +656,7 @@
     <row r="1" ht="35.1" customHeight="1" s="24">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SyncGuard AI 구축 프로젝트 연락망</t>
+          <t>한빛글로벌 SyncGuard AI 구축 프로젝트 연락망</t>
         </is>
       </c>
     </row>
@@ -722,13 +722,13 @@
       </c>
       <c r="C5" s="10" t="inlineStr">
         <is>
-          <t>㈜아모레퍼시픽
+          <t>㈜한빛글로벌
 연구전략 Lab</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
         <is>
-          <t>박주열</t>
+          <t>정민수</t>
         </is>
       </c>
       <c r="E5" s="8" t="inlineStr">
@@ -768,13 +768,13 @@
       </c>
       <c r="C6" s="14" t="inlineStr">
         <is>
-          <t>㈜아모레퍼시픽
+          <t>㈜한빛글로벌
 ERP플랫폼기획팀</t>
         </is>
       </c>
       <c r="D6" s="15" t="inlineStr">
         <is>
-          <t>김경호</t>
+          <t>한승우</t>
         </is>
       </c>
       <c r="E6" s="13" t="inlineStr">
@@ -814,13 +814,13 @@
       </c>
       <c r="C7" s="10" t="inlineStr">
         <is>
-          <t>㈜아모레퍼시픽
+          <t>㈜한빛글로벌
 RA Lab</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
         <is>
-          <t>양서윤</t>
+          <t>최윤아</t>
         </is>
       </c>
       <c r="E7" s="8" t="inlineStr">
@@ -830,7 +830,7 @@
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>화장품 표시광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
+          <t>제품 표시·광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -860,13 +860,13 @@
       </c>
       <c r="C8" s="14" t="inlineStr">
         <is>
-          <t>㈜아모레퍼시픽
+          <t>㈜한빛글로벌
 RA Lab</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
         <is>
-          <t>오혜주</t>
+          <t>윤서연</t>
         </is>
       </c>
       <c r="E8" s="13" t="inlineStr">
@@ -876,7 +876,7 @@
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>화장품 표시광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
+          <t>제품 표시·광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
@@ -906,13 +906,13 @@
       </c>
       <c r="C9" s="10" t="inlineStr">
         <is>
-          <t>㈜아모레퍼시픽
+          <t>㈜한빛글로벌
 RA Lab</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
         <is>
-          <t>김다은</t>
+          <t>배수빈</t>
         </is>
       </c>
       <c r="E9" s="8" t="inlineStr">
@@ -922,7 +922,7 @@
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>화장품 표시광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
+          <t>제품 표시·광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -952,13 +952,13 @@
       </c>
       <c r="C10" s="14" t="inlineStr">
         <is>
-          <t>㈜아모레퍼시픽
+          <t>㈜한빛글로벌
 RA Lab</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
         <is>
-          <t>장원희</t>
+          <t>송하늘</t>
         </is>
       </c>
       <c r="E10" s="13" t="inlineStr">
@@ -968,7 +968,7 @@
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>화장품 표시광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
+          <t>제품 표시·광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -998,12 +998,12 @@
       </c>
       <c r="C11" s="10" t="inlineStr">
         <is>
-          <t>㈜그로브소프트</t>
+          <t>㈜엠파시</t>
         </is>
       </c>
       <c r="D11" s="11" t="inlineStr">
         <is>
-          <t>오병문</t>
+          <t>박준혁</t>
         </is>
       </c>
       <c r="E11" s="8" t="inlineStr">
@@ -1043,12 +1043,12 @@
       </c>
       <c r="C12" s="14" t="inlineStr">
         <is>
-          <t>㈜그로브소프트</t>
+          <t>㈜엠파시</t>
         </is>
       </c>
       <c r="D12" s="15" t="inlineStr">
         <is>
-          <t>김재은</t>
+          <t>김태윤</t>
         </is>
       </c>
       <c r="E12" s="13" t="inlineStr">
@@ -1088,12 +1088,12 @@
       </c>
       <c r="C13" s="10" t="inlineStr">
         <is>
-          <t>㈜그로브소프트</t>
+          <t>㈜엠파시</t>
         </is>
       </c>
       <c r="D13" s="11" t="inlineStr">
         <is>
-          <t>황자영</t>
+          <t>이지훈</t>
         </is>
       </c>
       <c r="E13" s="8" t="inlineStr">
@@ -1133,12 +1133,12 @@
       </c>
       <c r="C14" s="14" t="inlineStr">
         <is>
-          <t>㈜그로브소프트</t>
+          <t>㈜엠파시</t>
         </is>
       </c>
       <c r="D14" s="15" t="inlineStr">
         <is>
-          <t>장지용</t>
+          <t>최현우</t>
         </is>
       </c>
       <c r="E14" s="13" t="inlineStr">
@@ -1178,12 +1178,12 @@
       </c>
       <c r="C15" s="14" t="inlineStr">
         <is>
-          <t>㈜아이시프트</t>
+          <t>㈜데이터브릿지</t>
         </is>
       </c>
       <c r="D15" s="15" t="inlineStr">
         <is>
-          <t>남석현</t>
+          <t>강동현</t>
         </is>
       </c>
       <c r="E15" s="13" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="C16" s="10" t="inlineStr">
         <is>
-          <t>㈜아이시프트</t>
+          <t>㈜데이터브릿지</t>
         </is>
       </c>
       <c r="D16" s="11" t="inlineStr">
         <is>
-          <t>진경민</t>
+          <t>조성민</t>
         </is>
       </c>
       <c r="E16" s="8" t="inlineStr">
@@ -1238,7 +1238,7 @@
       </c>
       <c r="F16" s="10" t="inlineStr">
         <is>
-          <t>아이시프트 과제 총괄 관리 및 리소스 조율</t>
+          <t>데이터브릿지 과제 총괄 관리 및 리소스 조율</t>
         </is>
       </c>
       <c r="G16" s="12" t="inlineStr">
@@ -1338,7 +1338,7 @@
       </c>
       <c r="C5" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 본사 회의실 / 화상 병행</t>
+          <t>한빛글로벌 본사 회의실 / 화상 병행</t>
         </is>
       </c>
       <c r="D5" s="4" t="inlineStr">
@@ -1365,7 +1365,7 @@
       </c>
       <c r="C6" s="6" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 연구소 / 본사</t>
+          <t>한빛글로벌 연구소 / 본사</t>
         </is>
       </c>
       <c r="D6" s="6" t="inlineStr">
@@ -1392,7 +1392,7 @@
       </c>
       <c r="C7" s="4" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 본사 회의실</t>
+          <t>한빛글로벌 본사 회의실</t>
         </is>
       </c>
       <c r="D7" s="4" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="C8" s="6" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 본사 회의실</t>
+          <t>한빛글로벌 본사 회의실</t>
         </is>
       </c>
       <c r="D8" s="6" t="inlineStr">
@@ -1486,7 +1486,7 @@
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 박주열 PM / 수행사 김재은 PM</t>
+          <t>한빛글로벌 정민수 PM / 수행사 김태윤 PM</t>
         </is>
       </c>
       <c r="E12" s="6" t="inlineStr">
@@ -1513,7 +1513,7 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>그로브소프트 PMO</t>
+          <t>엠파시 PMO</t>
         </is>
       </c>
       <c r="E13" s="4" t="inlineStr">
@@ -1535,12 +1535,12 @@
       </c>
       <c r="C14" s="6" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 SSO 통합 계정 체계</t>
+          <t>한빛글로벌 SSO 통합 계정 체계</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>아모레퍼시픽 기술 PM (김경호)</t>
+          <t>한빛글로벌 기술 PM (한승우)</t>
         </is>
       </c>
       <c r="E14" s="6" t="inlineStr">
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>클레임 AI 소스코드 및 문서 버전 관리</t>
+          <t>SyncGuard AI 소스코드 및 문서 버전 관리</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
@@ -1567,7 +1567,7 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>수행사 개발 리드 (김재은)</t>
+          <t>수행사 개발 리드 (김태윤)</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">

--- a/public/templates/office/EMP_MAN_005_프로젝트_연락처_및_회의체계.xlsx
+++ b/public/templates/office/EMP_MAN_005_프로젝트_연락처_및_회의체계.xlsx
@@ -656,7 +656,7 @@
     <row r="1" ht="35.1" customHeight="1" s="24">
       <c r="A1" s="23" t="inlineStr">
         <is>
-          <t>한빛글로벌 SyncGuard AI 구축 프로젝트 연락망</t>
+          <t>한빛글로벌 SyncFlow AI 구축 프로젝트 연락망</t>
         </is>
       </c>
     </row>
@@ -723,7 +723,7 @@
       <c r="C5" s="10" t="inlineStr">
         <is>
           <t>㈜한빛글로벌
-연구전략 Lab</t>
+공급망혁신팀</t>
         </is>
       </c>
       <c r="D5" s="11" t="inlineStr">
@@ -784,7 +784,7 @@
       </c>
       <c r="F6" s="14" t="inlineStr">
         <is>
-          <t>IT 시스템 인프라 총괄, ProductLab / 사내 연계 지원</t>
+          <t>IT 시스템 인프라 총괄, PLM-Nexus / 사내 연계 지원</t>
         </is>
       </c>
       <c r="G6" s="16" t="inlineStr">
@@ -815,7 +815,7 @@
       <c r="C7" s="10" t="inlineStr">
         <is>
           <t>㈜한빛글로벌
-RA Lab</t>
+품질법무검증팀</t>
         </is>
       </c>
       <c r="D7" s="11" t="inlineStr">
@@ -825,12 +825,12 @@
       </c>
       <c r="E7" s="8" t="inlineStr">
         <is>
-          <t>RA 실무 담당</t>
+          <t>QA 실무 담당</t>
         </is>
       </c>
       <c r="F7" s="10" t="inlineStr">
         <is>
-          <t>제품 표시·광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
+          <t>구매계약·기술규격 검증 기준 정의, 골든셋 검증, 파일럿 참여</t>
         </is>
       </c>
       <c r="G7" s="12" t="inlineStr">
@@ -845,7 +845,7 @@
       </c>
       <c r="I7" s="8" t="inlineStr">
         <is>
-          <t>RA팀</t>
+          <t>QA팀</t>
         </is>
       </c>
     </row>
@@ -861,7 +861,7 @@
       <c r="C8" s="14" t="inlineStr">
         <is>
           <t>㈜한빛글로벌
-RA Lab</t>
+품질법무검증팀</t>
         </is>
       </c>
       <c r="D8" s="15" t="inlineStr">
@@ -871,12 +871,12 @@
       </c>
       <c r="E8" s="13" t="inlineStr">
         <is>
-          <t>RA 실무 담당</t>
+          <t>QA 실무 담당</t>
         </is>
       </c>
       <c r="F8" s="14" t="inlineStr">
         <is>
-          <t>제품 표시·광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
+          <t>구매계약·기술규격 검증 기준 정의, 골든셋 검증, 파일럿 참여</t>
         </is>
       </c>
       <c r="G8" s="16" t="inlineStr">
@@ -891,7 +891,7 @@
       </c>
       <c r="I8" s="13" t="inlineStr">
         <is>
-          <t>RA팀</t>
+          <t>QA팀</t>
         </is>
       </c>
     </row>
@@ -907,7 +907,7 @@
       <c r="C9" s="10" t="inlineStr">
         <is>
           <t>㈜한빛글로벌
-RA Lab</t>
+품질법무검증팀</t>
         </is>
       </c>
       <c r="D9" s="11" t="inlineStr">
@@ -917,12 +917,12 @@
       </c>
       <c r="E9" s="8" t="inlineStr">
         <is>
-          <t>RA 실무 담당</t>
+          <t>QA 실무 담당</t>
         </is>
       </c>
       <c r="F9" s="10" t="inlineStr">
         <is>
-          <t>제품 표시·광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
+          <t>구매계약·기술규격 검증 기준 정의, 골든셋 검증, 파일럿 참여</t>
         </is>
       </c>
       <c r="G9" s="12" t="inlineStr">
@@ -937,7 +937,7 @@
       </c>
       <c r="I9" s="8" t="inlineStr">
         <is>
-          <t>RA팀</t>
+          <t>QA팀</t>
         </is>
       </c>
     </row>
@@ -953,7 +953,7 @@
       <c r="C10" s="14" t="inlineStr">
         <is>
           <t>㈜한빛글로벌
-RA Lab</t>
+품질법무검증팀</t>
         </is>
       </c>
       <c r="D10" s="15" t="inlineStr">
@@ -963,12 +963,12 @@
       </c>
       <c r="E10" s="13" t="inlineStr">
         <is>
-          <t>RA 실무 담당</t>
+          <t>QA 실무 담당</t>
         </is>
       </c>
       <c r="F10" s="14" t="inlineStr">
         <is>
-          <t>제품 표시·광고 심의 기준 정의, 골든셋 검증, 파일럿 참여</t>
+          <t>구매계약·기술규격 검증 기준 정의, 골든셋 검증, 파일럿 참여</t>
         </is>
       </c>
       <c r="G10" s="16" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="I10" s="13" t="inlineStr">
         <is>
-          <t>RA팀</t>
+          <t>QA팀</t>
         </is>
       </c>
     </row>
@@ -1148,7 +1148,7 @@
       </c>
       <c r="F14" s="14" t="inlineStr">
         <is>
-          <t>풀스택 웹 포털 개발, 시안 대조 뷰어, 백엔드 연계</t>
+          <t>풀스택 웹 포털 개발, 계약·도서 대조 뷰어, 백엔드 연계</t>
         </is>
       </c>
       <c r="G14" s="19" t="inlineStr">
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E15" s="13" t="inlineStr">
         <is>
-          <t>수석 / 실증DB 리드</t>
+          <t>수석 / 시험검증DB 리드</t>
         </is>
       </c>
       <c r="F15" s="14" t="inlineStr">
         <is>
-          <t>ProductLab 실증 데이터 DB 구축 및 연계 인터페이스 설계</t>
+          <t>PLM-Nexus 시험검증 데이터 DB 구축 및 연계 인터페이스 설계</t>
         </is>
       </c>
       <c r="G15" s="16" t="inlineStr">
@@ -1208,7 +1208,7 @@
       </c>
       <c r="I15" s="13" t="inlineStr">
         <is>
-          <t>실증 DB / 연계</t>
+          <t>시험검증 DB / 연계</t>
         </is>
       </c>
     </row>
@@ -1286,7 +1286,7 @@
     <row r="1" ht="32.1" customHeight="1" s="24">
       <c r="A1" s="27" t="inlineStr">
         <is>
-          <t>SyncGuard AI 프로젝트 정례 회의 및 협업 채널 안내</t>
+          <t>SyncFlow AI 프로젝트 정례 회의 및 협업 채널 안내</t>
         </is>
       </c>
     </row>
@@ -1343,12 +1343,12 @@
       </c>
       <c r="D5" s="4" t="inlineStr">
         <is>
-          <t>발주사 PM/RA 전원, 수행사 핵심진</t>
+          <t>발주사 PM/QA 전원, 수행사 핵심진</t>
         </is>
       </c>
       <c r="E5" s="4" t="inlineStr">
         <is>
-          <t>차주 계획 공유, 심의 기준 및 UI/UX 피드백, 이슈 점검</t>
+          <t>차주 계획 공유, 검증 기준 및 UI/UX 피드백, 이슈 점검</t>
         </is>
       </c>
     </row>
@@ -1375,7 +1375,7 @@
       </c>
       <c r="E6" s="6" t="inlineStr">
         <is>
-          <t>사내 SSO(IAM), MarketingHub, ProductLab 연계 규격 및 네트워크 협의</t>
+          <t>사내 SSO(IAM), SRM-Portal, PLM-Nexus 연계 규격 및 네트워크 협의</t>
         </is>
       </c>
     </row>
@@ -1557,7 +1557,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>SyncGuard AI 소스코드 및 문서 버전 관리</t>
+          <t>SyncFlow AI 소스코드 및 문서 버전 관리</t>
         </is>
       </c>
       <c r="C15" s="4" t="inlineStr">
